--- a/work_agents/Aria - Process Engineer/deliverables/1-CAL-XXXX.xlsx
+++ b/work_agents/Aria - Process Engineer/deliverables/1-CAL-XXXX.xlsx
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="C13" s="13" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="C14" s="13" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>Monoethylene Glycol (MEG) requires corrosion inhibition, especially at elevated temperatures and in the presence of oxygen, to prevent degradation and the formation of corrosive organic acids. It is also hygroscopic and can absorb water from the atmosphere.</t>
+          <t>MEG is hygroscopic and can degrade to corrosive organic acids (e.g., glycolic acid) over time, especially in the presence of oxygen and high temperatures. Inhibition is often required for long-term use in carbon steel systems. Ensure proper material selection and monitoring.</t>
         </is>
       </c>
       <c r="D16" s="16" t="inlineStr">
@@ -1652,7 +1652,7 @@
     <row r="50">
       <c r="A50" s="27" t="inlineStr">
         <is>
-          <t>Generated by Process Engineer Agent (Aria)  |  2026-04-02T18:32:46  |  A Star Chemical</t>
+          <t>Generated by Process Engineer Agent (Aria)  |  2026-04-02T23:09:13  |  A Star Chemical</t>
         </is>
       </c>
     </row>

--- a/work_agents/Aria - Process Engineer/deliverables/1-CAL-XXXX.xlsx
+++ b/work_agents/Aria - Process Engineer/deliverables/1-CAL-XXXX.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Sarnia, Ontario, Canada</t>
+          <t>Sarnia, Canada</t>
         </is>
       </c>
       <c r="C5" s="7" t="n"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C6" s="7" t="n"/>
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="C13" s="13" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="C14" s="13" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>MEG is hygroscopic and can degrade to corrosive organic acids (e.g., glycolic acid) over time, especially in the presence of oxygen and high temperatures. Inhibition is often required for long-term use in carbon steel systems. Ensure proper material selection and monitoring.</t>
+          <t>MEG is hygroscopic and can degrade to corrosive organic acids (e.g., glycolic acid) at elevated temperatures or in the presence of oxygen. Proper inhibition and material selection are crucial to prevent corrosion. Viscosity and vapor pressure are engineering estimates for 95% MEG at 65 °C.</t>
         </is>
       </c>
       <c r="D16" s="16" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="C31" s="13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
       <c r="E31" s="14" t="inlineStr"/>
       <c r="F31" s="14" t="inlineStr">
         <is>
-          <t>Source: 5-LST-0003</t>
+          <t>Source: 5-LST-0003-2</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
     <row r="50">
       <c r="A50" s="27" t="inlineStr">
         <is>
-          <t>Generated by Process Engineer Agent (Aria)  |  2026-04-02T23:09:13  |  A Star Chemical</t>
+          <t>Generated by Process Engineer Agent (Aria)  |  2026-04-28T04:08:00  |  A Star Chemical</t>
         </is>
       </c>
     </row>
